--- a/data/gravel/Van Nicholas Rowtag 2025.xlsx
+++ b/data/gravel/Van Nicholas Rowtag 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11214"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5EAB10C-8E9B-414F-A10D-B2B98B6908D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B3FB75F0-D4DF-294F-B6A1-0DCBFE82C469}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32440" yWindow="-26380" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4140" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="127">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="137" uniqueCount="129">
   <si>
     <t>brand</t>
   </si>
@@ -414,6 +414,12 @@
   </si>
   <si>
     <t>1.125 - 1.5</t>
+  </si>
+  <si>
+    <t>IS42</t>
+  </si>
+  <si>
+    <t>IS52</t>
   </si>
 </sst>
 </file>
@@ -1591,16 +1597,16 @@
       <c r="A54" t="s">
         <v>77</v>
       </c>
-      <c r="B54">
-        <v>42</v>
+      <c r="B54" s="1" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>78</v>
       </c>
-      <c r="B55">
-        <v>52.1</v>
+      <c r="B55" s="1" t="s">
+        <v>128</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
